--- a/GATEWAY/A1#111#CODEBYTESRLXX/CODEBYTESRL/codebyte.medisolution/2026.03/accreditamento-checklist_V8.3.0.xlsx
+++ b/GATEWAY/A1#111#CODEBYTESRLXX/CODEBYTESRL/codebyte.medisolution/2026.03/accreditamento-checklist_V8.3.0.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="176">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -365,6 +365,15 @@
     <t>SI</t>
   </si>
   <si>
+    <t>SI è verificato un errore durante l’invio del referto a FSE: &lt;messaggio errore ricevuto&gt;</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>Il messaggio viene visualizzato all’utente per avvisare dell’errore e permettere il rinvio del referto</t>
+  </si>
+  <si>
     <t>KO</t>
   </si>
   <si>
@@ -475,9 +484,6 @@
       <t xml:space="preserve">
 </t>
     </r>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>VALIDAZIONE_RSA_TIMEOUT</t>
@@ -3457,17 +3463,29 @@
       <c r="M10" t="s" s="56">
         <v>56</v>
       </c>
-      <c r="N10" s="57"/>
-      <c r="O10" s="57"/>
-      <c r="P10" s="57"/>
-      <c r="Q10" s="57"/>
-      <c r="R10" s="57"/>
-      <c r="S10" s="57"/>
+      <c r="N10" t="s" s="56">
+        <v>56</v>
+      </c>
+      <c r="O10" t="s" s="56">
+        <v>57</v>
+      </c>
+      <c r="P10" t="s" s="56">
+        <v>56</v>
+      </c>
+      <c r="Q10" t="s" s="56">
+        <v>58</v>
+      </c>
+      <c r="R10" t="s" s="56">
+        <v>58</v>
+      </c>
+      <c r="S10" t="s" s="56">
+        <v>59</v>
+      </c>
       <c r="T10" s="57"/>
       <c r="U10" s="56"/>
       <c r="V10" s="58"/>
       <c r="W10" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" ht="11.15" customHeight="1">
@@ -3481,10 +3499,10 @@
         <v>51</v>
       </c>
       <c r="D11" t="s" s="51">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s" s="52">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F11" s="53">
         <v>46097</v>
@@ -3493,10 +3511,10 @@
         <v>46097.892511574071</v>
       </c>
       <c r="H11" t="s" s="55">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I11" t="s" s="59">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J11" t="s" s="56">
         <v>56</v>
@@ -3509,20 +3527,26 @@
       <c r="N11" t="s" s="56">
         <v>56</v>
       </c>
-      <c r="O11" s="57"/>
+      <c r="O11" t="s" s="56">
+        <v>57</v>
+      </c>
       <c r="P11" t="s" s="56">
         <v>56</v>
       </c>
       <c r="Q11" t="s" s="56">
-        <v>62</v>
-      </c>
-      <c r="R11" s="57"/>
-      <c r="S11" s="57"/>
+        <v>58</v>
+      </c>
+      <c r="R11" t="s" s="56">
+        <v>58</v>
+      </c>
+      <c r="S11" t="s" s="56">
+        <v>59</v>
+      </c>
       <c r="T11" s="57"/>
       <c r="U11" s="56"/>
       <c r="V11" s="58"/>
       <c r="W11" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" ht="11.15" customHeight="1">
@@ -3536,10 +3560,10 @@
         <v>51</v>
       </c>
       <c r="D12" t="s" s="51">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s" s="52">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F12" s="53"/>
       <c r="G12" s="54"/>
@@ -3556,24 +3580,28 @@
       <c r="N12" t="s" s="56">
         <v>56</v>
       </c>
-      <c r="O12" s="57"/>
+      <c r="O12" t="s" s="56">
+        <v>57</v>
+      </c>
       <c r="P12" t="s" s="56">
         <v>56</v>
       </c>
       <c r="Q12" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="R12" t="s" s="56">
-        <v>62</v>
-      </c>
-      <c r="S12" s="57"/>
+        <v>58</v>
+      </c>
+      <c r="S12" t="s" s="56">
+        <v>59</v>
+      </c>
       <c r="T12" s="57"/>
       <c r="U12" t="s" s="56">
         <v>56</v>
       </c>
       <c r="V12" s="58"/>
       <c r="W12" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" ht="11.15" customHeight="1">
@@ -3587,10 +3615,10 @@
         <v>51</v>
       </c>
       <c r="D13" t="s" s="51">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s" s="52">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F13" s="53">
         <v>46097</v>
@@ -3599,10 +3627,10 @@
         <v>46097.898831018516</v>
       </c>
       <c r="H13" t="s" s="55">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I13" t="s" s="55">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J13" t="s" s="56">
         <v>56</v>
@@ -3615,22 +3643,26 @@
       <c r="N13" t="s" s="56">
         <v>56</v>
       </c>
-      <c r="O13" s="57"/>
+      <c r="O13" t="s" s="56">
+        <v>57</v>
+      </c>
       <c r="P13" t="s" s="56">
         <v>56</v>
       </c>
       <c r="Q13" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="R13" t="s" s="56">
-        <v>62</v>
-      </c>
-      <c r="S13" s="57"/>
+        <v>58</v>
+      </c>
+      <c r="S13" t="s" s="56">
+        <v>59</v>
+      </c>
       <c r="T13" s="57"/>
       <c r="U13" s="56"/>
       <c r="V13" s="58"/>
       <c r="W13" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" ht="11.15" customHeight="1">
@@ -3644,20 +3676,20 @@
         <v>51</v>
       </c>
       <c r="D14" t="s" s="51">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s" s="52">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F14" s="53"/>
       <c r="G14" s="54"/>
       <c r="H14" s="53"/>
       <c r="I14" s="53"/>
       <c r="J14" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K14" t="s" s="56">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L14" s="57"/>
       <c r="M14" s="57"/>
@@ -3671,7 +3703,7 @@
       <c r="U14" s="56"/>
       <c r="V14" s="58"/>
       <c r="W14" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" ht="11.15" customHeight="1">
@@ -3685,20 +3717,20 @@
         <v>51</v>
       </c>
       <c r="D15" t="s" s="51">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s" s="52">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F15" s="53"/>
       <c r="G15" s="54"/>
       <c r="H15" s="53"/>
       <c r="I15" s="53"/>
       <c r="J15" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K15" t="s" s="56">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L15" s="57"/>
       <c r="M15" s="57"/>
@@ -3712,7 +3744,7 @@
       <c r="U15" s="56"/>
       <c r="V15" s="58"/>
       <c r="W15" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="11.15" customHeight="1">
@@ -3726,10 +3758,10 @@
         <v>51</v>
       </c>
       <c r="D16" t="s" s="51">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s" s="52">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F16" s="53">
         <v>46097</v>
@@ -3738,10 +3770,10 @@
         <v>46097.913935185185</v>
       </c>
       <c r="H16" t="s" s="55">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s" s="55">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J16" t="s" s="56">
         <v>56</v>
@@ -3754,22 +3786,26 @@
       <c r="N16" t="s" s="56">
         <v>56</v>
       </c>
-      <c r="O16" s="57"/>
+      <c r="O16" t="s" s="56">
+        <v>57</v>
+      </c>
       <c r="P16" t="s" s="56">
         <v>56</v>
       </c>
       <c r="Q16" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="R16" t="s" s="56">
-        <v>62</v>
-      </c>
-      <c r="S16" s="57"/>
+        <v>58</v>
+      </c>
+      <c r="S16" t="s" s="56">
+        <v>59</v>
+      </c>
       <c r="T16" s="57"/>
       <c r="U16" s="56"/>
       <c r="V16" s="58"/>
       <c r="W16" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" ht="11.15" customHeight="1">
@@ -3783,20 +3819,20 @@
         <v>51</v>
       </c>
       <c r="D17" t="s" s="51">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s" s="52">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="54"/>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
       <c r="J17" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K17" t="s" s="56">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L17" s="57"/>
       <c r="M17" s="57"/>
@@ -3810,7 +3846,7 @@
       <c r="U17" s="56"/>
       <c r="V17" s="58"/>
       <c r="W17" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" ht="11.15" customHeight="1">
@@ -3824,10 +3860,10 @@
         <v>51</v>
       </c>
       <c r="D18" t="s" s="51">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s" s="52">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="53">
         <v>46097</v>
@@ -3836,10 +3872,10 @@
         <v>46097.917337962965</v>
       </c>
       <c r="H18" t="s" s="55">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I18" t="s" s="55">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J18" t="s" s="56">
         <v>56</v>
@@ -3852,22 +3888,26 @@
       <c r="N18" t="s" s="56">
         <v>56</v>
       </c>
-      <c r="O18" s="57"/>
+      <c r="O18" t="s" s="56">
+        <v>57</v>
+      </c>
       <c r="P18" t="s" s="56">
         <v>56</v>
       </c>
       <c r="Q18" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="R18" t="s" s="56">
-        <v>62</v>
-      </c>
-      <c r="S18" s="57"/>
+        <v>58</v>
+      </c>
+      <c r="S18" t="s" s="56">
+        <v>59</v>
+      </c>
       <c r="T18" s="57"/>
       <c r="U18" s="56"/>
       <c r="V18" s="58"/>
       <c r="W18" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" ht="11.15" customHeight="1">
@@ -3881,20 +3921,20 @@
         <v>51</v>
       </c>
       <c r="D19" t="s" s="51">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s" s="52">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F19" s="53"/>
       <c r="G19" s="54"/>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
       <c r="J19" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K19" t="s" s="56">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L19" s="57"/>
       <c r="M19" s="57"/>
@@ -3908,7 +3948,7 @@
       <c r="U19" s="56"/>
       <c r="V19" s="58"/>
       <c r="W19" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" ht="11.15" customHeight="1">
@@ -3922,20 +3962,20 @@
         <v>51</v>
       </c>
       <c r="D20" t="s" s="51">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s" s="52">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F20" s="53"/>
       <c r="G20" s="54"/>
       <c r="H20" s="53"/>
       <c r="I20" s="53"/>
       <c r="J20" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K20" t="s" s="56">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L20" s="57"/>
       <c r="M20" s="57"/>
@@ -3949,7 +3989,7 @@
       <c r="U20" s="56"/>
       <c r="V20" s="58"/>
       <c r="W20" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" ht="11.15" customHeight="1">
@@ -3963,10 +4003,10 @@
         <v>51</v>
       </c>
       <c r="D21" t="s" s="51">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s" s="52">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F21" s="53">
         <v>46097</v>
@@ -3975,10 +4015,10 @@
         <v>46097.922013888892</v>
       </c>
       <c r="H21" t="s" s="55">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I21" t="s" s="55">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J21" t="s" s="56">
         <v>56</v>
@@ -3991,22 +4031,26 @@
       <c r="N21" t="s" s="56">
         <v>56</v>
       </c>
-      <c r="O21" s="57"/>
+      <c r="O21" t="s" s="56">
+        <v>57</v>
+      </c>
       <c r="P21" t="s" s="56">
         <v>56</v>
       </c>
       <c r="Q21" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="R21" t="s" s="56">
-        <v>62</v>
-      </c>
-      <c r="S21" s="57"/>
+        <v>58</v>
+      </c>
+      <c r="S21" t="s" s="56">
+        <v>59</v>
+      </c>
       <c r="T21" s="57"/>
       <c r="U21" s="56"/>
       <c r="V21" s="58"/>
       <c r="W21" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" ht="11.15" customHeight="1">
@@ -4020,20 +4064,20 @@
         <v>51</v>
       </c>
       <c r="D22" t="s" s="51">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s" s="52">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F22" s="53"/>
       <c r="G22" s="54"/>
       <c r="H22" s="53"/>
       <c r="I22" s="53"/>
       <c r="J22" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K22" t="s" s="56">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L22" s="57"/>
       <c r="M22" s="57"/>
@@ -4047,7 +4091,7 @@
       <c r="U22" s="56"/>
       <c r="V22" s="58"/>
       <c r="W22" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" ht="11.15" customHeight="1">
@@ -4061,20 +4105,20 @@
         <v>51</v>
       </c>
       <c r="D23" t="s" s="51">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E23" t="s" s="52">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F23" s="53"/>
       <c r="G23" s="54"/>
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
       <c r="J23" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K23" t="s" s="56">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L23" s="57"/>
       <c r="M23" s="57"/>
@@ -4088,7 +4132,7 @@
       <c r="U23" s="56"/>
       <c r="V23" s="58"/>
       <c r="W23" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" ht="11.15" customHeight="1">
@@ -4102,20 +4146,20 @@
         <v>51</v>
       </c>
       <c r="D24" t="s" s="51">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s" s="52">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F24" s="53"/>
       <c r="G24" s="54"/>
       <c r="H24" s="53"/>
       <c r="I24" s="53"/>
       <c r="J24" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K24" t="s" s="56">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L24" s="57"/>
       <c r="M24" s="57"/>
@@ -4129,7 +4173,7 @@
       <c r="U24" s="56"/>
       <c r="V24" s="58"/>
       <c r="W24" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" ht="11.15" customHeight="1">
@@ -4143,20 +4187,20 @@
         <v>51</v>
       </c>
       <c r="D25" t="s" s="51">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E25" t="s" s="52">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F25" s="53"/>
       <c r="G25" s="54"/>
       <c r="H25" s="53"/>
       <c r="I25" s="53"/>
       <c r="J25" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K25" t="s" s="56">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L25" s="57"/>
       <c r="M25" s="57"/>
@@ -4170,7 +4214,7 @@
       <c r="U25" s="56"/>
       <c r="V25" s="58"/>
       <c r="W25" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" ht="11.15" customHeight="1">
@@ -4184,20 +4228,20 @@
         <v>51</v>
       </c>
       <c r="D26" t="s" s="51">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s" s="52">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="54"/>
       <c r="H26" s="53"/>
       <c r="I26" s="53"/>
       <c r="J26" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K26" t="s" s="56">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L26" s="57"/>
       <c r="M26" s="57"/>
@@ -4211,7 +4255,7 @@
       <c r="U26" s="56"/>
       <c r="V26" s="58"/>
       <c r="W26" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" ht="11.15" customHeight="1">
@@ -4225,20 +4269,20 @@
         <v>51</v>
       </c>
       <c r="D27" t="s" s="51">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s" s="52">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F27" s="53"/>
       <c r="G27" s="54"/>
       <c r="H27" s="53"/>
       <c r="I27" s="53"/>
       <c r="J27" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K27" t="s" s="56">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L27" s="57"/>
       <c r="M27" s="57"/>
@@ -4252,7 +4296,7 @@
       <c r="U27" s="56"/>
       <c r="V27" s="58"/>
       <c r="W27" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" ht="11.15" customHeight="1">
@@ -4266,10 +4310,10 @@
         <v>51</v>
       </c>
       <c r="D28" t="s" s="51">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s" s="52">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F28" s="53">
         <v>46097</v>
@@ -4278,10 +4322,10 @@
         <v>46097.885532407410</v>
       </c>
       <c r="H28" t="s" s="61">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I28" t="s" s="61">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J28" t="s" s="56">
         <v>56</v>
@@ -4294,22 +4338,26 @@
       <c r="N28" t="s" s="56">
         <v>56</v>
       </c>
-      <c r="O28" s="57"/>
+      <c r="O28" t="s" s="56">
+        <v>57</v>
+      </c>
       <c r="P28" t="s" s="56">
         <v>56</v>
       </c>
       <c r="Q28" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="R28" t="s" s="56">
-        <v>62</v>
-      </c>
-      <c r="S28" s="57"/>
+        <v>58</v>
+      </c>
+      <c r="S28" t="s" s="56">
+        <v>59</v>
+      </c>
       <c r="T28" s="57"/>
       <c r="U28" s="56"/>
       <c r="V28" s="58"/>
       <c r="W28" t="s" s="56">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" ht="11.15" customHeight="1">
@@ -4323,10 +4371,10 @@
         <v>51</v>
       </c>
       <c r="D29" t="s" s="51">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E29" t="s" s="52">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F29" s="53">
         <v>46097</v>
@@ -4335,10 +4383,10 @@
         <v>46097.8840625</v>
       </c>
       <c r="H29" t="s" s="61">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I29" t="s" s="61">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J29" t="s" s="56">
         <v>56</v>
@@ -4351,22 +4399,26 @@
       <c r="N29" t="s" s="56">
         <v>56</v>
       </c>
-      <c r="O29" s="57"/>
+      <c r="O29" t="s" s="56">
+        <v>57</v>
+      </c>
       <c r="P29" t="s" s="56">
         <v>56</v>
       </c>
       <c r="Q29" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="R29" t="s" s="56">
-        <v>62</v>
-      </c>
-      <c r="S29" s="57"/>
+        <v>58</v>
+      </c>
+      <c r="S29" t="s" s="56">
+        <v>59</v>
+      </c>
       <c r="T29" s="57"/>
       <c r="U29" s="56"/>
       <c r="V29" s="58"/>
       <c r="W29" t="s" s="56">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
@@ -4380,20 +4432,20 @@
         <v>51</v>
       </c>
       <c r="D30" t="s" s="51">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E30" t="s" s="52">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F30" s="63"/>
       <c r="G30" s="64"/>
       <c r="H30" s="63"/>
       <c r="I30" s="63"/>
       <c r="J30" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K30" t="s" s="56">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L30" s="63"/>
       <c r="M30" s="57"/>
@@ -4407,7 +4459,7 @@
       <c r="U30" s="63"/>
       <c r="V30" s="63"/>
       <c r="W30" t="s" s="51">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
@@ -4421,20 +4473,20 @@
         <v>51</v>
       </c>
       <c r="D31" t="s" s="51">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s" s="52">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F31" s="63"/>
       <c r="G31" s="64"/>
       <c r="H31" s="63"/>
       <c r="I31" s="63"/>
       <c r="J31" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K31" t="s" s="56">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L31" s="63"/>
       <c r="M31" s="57"/>
@@ -4448,7 +4500,7 @@
       <c r="U31" s="63"/>
       <c r="V31" s="63"/>
       <c r="W31" t="s" s="51">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
@@ -4462,20 +4514,20 @@
         <v>51</v>
       </c>
       <c r="D32" t="s" s="51">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s" s="52">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F32" s="53"/>
       <c r="G32" s="54"/>
       <c r="H32" s="53"/>
       <c r="I32" s="53"/>
       <c r="J32" t="s" s="56">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K32" t="s" s="56">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L32" s="57"/>
       <c r="M32" s="57"/>
@@ -4489,7 +4541,7 @@
       <c r="U32" s="56"/>
       <c r="V32" s="58"/>
       <c r="W32" t="s" s="56">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
@@ -17109,7 +17161,7 @@
   <sheetData>
     <row r="1" ht="13.55" customHeight="1">
       <c r="A1" t="s" s="71">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -17118,7 +17170,7 @@
     </row>
     <row r="2" ht="13.55" customHeight="1">
       <c r="A2" t="s" s="71">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -17127,7 +17179,7 @@
     </row>
     <row r="3" ht="13.55" customHeight="1">
       <c r="A3" t="s" s="71">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -17136,7 +17188,7 @@
     </row>
     <row r="4" ht="13.55" customHeight="1">
       <c r="A4" t="s" s="71">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -17145,7 +17197,7 @@
     </row>
     <row r="5" ht="13.55" customHeight="1">
       <c r="A5" t="s" s="71">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -17154,7 +17206,7 @@
     </row>
     <row r="6" ht="13.55" customHeight="1">
       <c r="A6" t="s" s="71">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -17163,7 +17215,7 @@
     </row>
     <row r="7" ht="13.55" customHeight="1">
       <c r="A7" t="s" s="71">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -17172,7 +17224,7 @@
     </row>
     <row r="8" ht="13.55" customHeight="1">
       <c r="A8" t="s" s="71">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -17219,37 +17271,37 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" t="s" s="73">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B1" t="s" s="73">
         <v>28</v>
       </c>
       <c r="C1" t="s" s="73">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D1" t="s" s="73">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E1" s="74"/>
       <c r="F1" t="s" s="75">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G1" t="s" s="76">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="s" s="77">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s" s="78">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C2" t="s" s="79">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s" s="79">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E2" s="30"/>
       <c r="F2" s="19"/>
@@ -17257,16 +17309,16 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" t="s" s="77">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s" s="78">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C3" t="s" s="79">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D3" t="s" s="79">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E3" s="30"/>
       <c r="F3" s="3"/>
@@ -17274,16 +17326,16 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" t="s" s="77">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s" s="78">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C4" t="s" s="79">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s" s="80">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E4" s="30"/>
       <c r="F4" s="3"/>
@@ -17291,16 +17343,16 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" t="s" s="77">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B5" t="s" s="78">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C5" t="s" s="79">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D5" t="s" s="79">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="3"/>
@@ -17308,16 +17360,16 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" t="s" s="77">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s" s="78">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C6" t="s" s="79">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D6" t="s" s="80">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E6" s="30"/>
       <c r="F6" s="3"/>
@@ -17325,16 +17377,16 @@
     </row>
     <row r="7" ht="14.5" customHeight="1">
       <c r="A7" t="s" s="77">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s" s="78">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s" s="79">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D7" t="s" s="80">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="3"/>
@@ -17345,13 +17397,13 @@
         <v>51</v>
       </c>
       <c r="B8" t="s" s="78">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C8" t="s" s="79">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D8" t="s" s="80">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E8" s="30"/>
       <c r="F8" s="3"/>
@@ -17359,16 +17411,16 @@
     </row>
     <row r="9" ht="14.5" customHeight="1">
       <c r="A9" t="s" s="77">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B9" t="s" s="78">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C9" t="s" s="79">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D9" t="s" s="80">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="3"/>
@@ -17376,16 +17428,16 @@
     </row>
     <row r="10" ht="43.5" customHeight="1">
       <c r="A10" t="s" s="77">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B10" t="s" s="78">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C10" t="s" s="80">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s" s="79">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E10" s="30"/>
       <c r="F10" s="3"/>
@@ -17393,16 +17445,16 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" t="s" s="77">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B11" t="s" s="78">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C11" t="s" s="79">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D11" t="s" s="80">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E11" s="30"/>
       <c r="F11" s="3"/>
@@ -17410,16 +17462,16 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" t="s" s="77">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B12" t="s" s="78">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C12" t="s" s="79">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D12" t="s" s="80">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E12" s="30"/>
       <c r="F12" s="3"/>
@@ -17427,16 +17479,16 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" t="s" s="77">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="78">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C13" t="s" s="79">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D13" t="s" s="80">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="3"/>
@@ -17444,16 +17496,16 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" t="s" s="77">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="78">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C14" t="s" s="79">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D14" t="s" s="80">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E14" s="30"/>
       <c r="F14" s="3"/>
@@ -17461,16 +17513,16 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" t="s" s="77">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="78">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C15" s="81">
         <v>521</v>
       </c>
       <c r="D15" t="s" s="80">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="3"/>
@@ -17509,7 +17561,7 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="s" s="86">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s" s="87">
         <v>56</v>
@@ -17520,10 +17572,10 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" t="s" s="86">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B3" t="s" s="87">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C3" s="85"/>
       <c r="D3" s="3"/>
